--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513300_ELIMINGRA12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513300_ELIMINGRA12FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3471</v>
+        <v>5.9759</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5283</v>
+        <v>5.4147</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8188</v>
+        <v>0.5612</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7268</v>
+        <v>3.8647</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3511</v>
+        <v>3.5125</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6243</v>
+        <v>0.3522</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1866</v>
+        <v>4.429</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1809</v>
+        <v>3.3663</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0057</v>
+        <v>1.0627</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4598</v>
+        <v>-0.5643</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1702</v>
+        <v>0.1461</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.63</v>
+        <v>-0.7104</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2003</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.8011</v>
+        <v>2.5316</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0196</v>
+        <v>-0.4204</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8227</v>
+        <v>-0.2353</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1969</v>
+        <v>-0.1851</v>
       </c>
       <c r="V2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7194</v>
+        <v>1.2211</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7194</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8685</v>
+        <v>5.4571</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3167</v>
+        <v>4.269</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5518999999999999</v>
+        <v>1.188</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7768</v>
+        <v>2.7338</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5136</v>
+        <v>3.3709</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2632</v>
+        <v>-0.6371</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1723</v>
+        <v>3.3704</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2791</v>
+        <v>3.2971</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8932</v>
+        <v>0.0733</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3955</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2345</v>
+        <v>0.0738</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.63</v>
+        <v>-0.7104</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6007</v>
+        <v>3.7</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.509</v>
+        <v>0.1917</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0554</v>
+        <v>0.287</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4536</v>
+        <v>-0.0953</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>1.78</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1998</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6444</v>
+        <v>4.575</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3359</v>
+        <v>2.0203</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3085</v>
+        <v>2.5547</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2774</v>
+        <v>2.3161</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3193</v>
+        <v>2.3811</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0419</v>
+        <v>-0.065</v>
       </c>
       <c r="J4" t="n">
-        <v>2.921</v>
+        <v>3.0292</v>
       </c>
       <c r="K4" t="n">
-        <v>2.841</v>
+        <v>2.9481</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6435</v>
+        <v>-0.7131</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5671</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7668</v>
+        <v>0.6747</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6446</v>
+        <v>-0.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4114</v>
+        <v>0.7946</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7269</v>
+        <v>3.1834</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5554</v>
+        <v>1.0022</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1715</v>
+        <v>2.1812</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1265</v>
+        <v>0.0246</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3572</v>
+        <v>3.415</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.4837</v>
+        <v>-3.3905</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3401</v>
+        <v>1.6705</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5226</v>
+        <v>3.6794</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.1826</v>
+        <v>-2.009</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4665</v>
+        <v>-1.6459</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1654</v>
+        <v>-0.2644</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3011</v>
+        <v>-1.3815</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R5" t="n">
-        <v>4.0011</v>
+        <v>3.8947</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8731</v>
+        <v>0.2047</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2362</v>
+        <v>0.2723</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3631</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1795</v>
+        <v>0.2279</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1795</v>
+        <v>0.2279</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0289</v>
+        <v>0.3126</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6079</v>
+        <v>0.906</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.5934</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1954</v>
+        <v>0.2092</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1797</v>
+        <v>1.2111</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9842</v>
+        <v>-1.0018</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7034</v>
+        <v>0.7842</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3014</v>
+        <v>1.3676</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.508</v>
+        <v>-0.5749</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3862</v>
+        <v>-0.4184</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S6" t="n">
-        <v>0.033</v>
+        <v>0.3507</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0955</v>
+        <v>0.1218</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1284</v>
+        <v>0.2289</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9163</v>
+        <v>-0.258</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8981</v>
+        <v>-2.8238</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9818</v>
+        <v>2.5658</v>
       </c>
       <c r="G7" t="n">
-        <v>0.763</v>
+        <v>-0.6521</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5337</v>
+        <v>-0.0216</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2293</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0872</v>
+        <v>-1.8298</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3635</v>
+        <v>-0.5413</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7237</v>
+        <v>-1.2885</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3242</v>
+        <v>1.1777</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1702</v>
+        <v>0.5198</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4944</v>
+        <v>0.6579</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2003</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0011</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8008</v>
+        <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2192</v>
+        <v>-0.1901</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0158</v>
+        <v>-0.0203</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2349</v>
+        <v>-0.1698</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9626</v>
+        <v>-0.6443</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.5189</v>
+        <v>-2.3838</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5563</v>
+        <v>1.7396</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6399</v>
+        <v>0.7109</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6311</v>
+        <v>0.2008</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.874</v>
+        <v>1.2146</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0.4363</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.316</v>
+        <v>0.7784</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2342</v>
+        <v>-0.5037</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5493</v>
+        <v>0.0738</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6849</v>
+        <v>-0.5775</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6002</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-3.8947</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6005</v>
+        <v>2.7263</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9229000000000001</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6446</v>
+        <v>0.2963</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2784</v>
+        <v>-0.2035</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8634</v>
+        <v>-2.3387</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.0462</v>
+        <v>-4.2923</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1828</v>
+        <v>1.9536</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4509</v>
+        <v>-1.47</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2022</v>
+        <v>-1.209</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2487</v>
+        <v>-0.261</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5701</v>
+        <v>-2.4899</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.894</v>
+        <v>-1.8498</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6761</v>
+        <v>-0.6401</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1192</v>
+        <v>1.0199</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6918</v>
+        <v>0.6409</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4274</v>
+        <v>0.379</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2127</v>
+        <v>0.3523</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2755</v>
+        <v>0.3397</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0127</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9908</v>
+        <v>-2.6295</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-0.6247</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9943</v>
+        <v>-2.0048</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4603</v>
+        <v>-1.4435</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1843</v>
+        <v>-0.1955</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.276</v>
+        <v>-1.248</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6742</v>
+        <v>-0.6146</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7542</v>
+        <v>-0.6967</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7861</v>
+        <v>-0.8289</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5218</v>
+        <v>-0.5513</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6711</v>
+        <v>-0.2697</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3223</v>
+        <v>-0.0101</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3488</v>
+        <v>-0.2596</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2853</v>
+        <v>-4.7574</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.9335</v>
+        <v>-5.9758</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6482</v>
+        <v>1.2184</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1318</v>
+        <v>-4.0964</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4716</v>
+        <v>-1.4414</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6602</v>
+        <v>-2.6551</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.201</v>
+        <v>-1.9729</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9707</v>
+        <v>-0.8388</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2303</v>
+        <v>-1.1341</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9308</v>
+        <v>-2.1235</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5009</v>
+        <v>-0.6025</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4299</v>
+        <v>-1.521</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.413</v>
+        <v>0.0332</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7911</v>
+        <v>-0.1929</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3781</v>
+        <v>0.2261</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.597399999999999</v>
+        <v>8.876100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.049</v>
+        <v>-2.4882</v>
       </c>
       <c r="F12" t="n">
-        <v>13.6464</v>
+        <v>11.3643</v>
       </c>
       <c r="G12" t="n">
-        <v>1.93</v>
+        <v>2.197299999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>11.3878</v>
+        <v>11.5331</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.457599999999999</v>
+        <v>-9.336</v>
       </c>
       <c r="J12" t="n">
-        <v>6.091299999999999</v>
+        <v>7.590700000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>11.1458</v>
+        <v>11.947</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.0546</v>
+        <v>-4.3564</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.161</v>
+        <v>-5.3933</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2418999999999999</v>
+        <v>-0.4137000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.403</v>
+        <v>-4.9796</v>
       </c>
       <c r="P12" t="n">
-        <v>9.002599999999999</v>
+        <v>8.763200000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.0041</v>
+        <v>-14.6052</v>
       </c>
       <c r="R12" t="n">
-        <v>24.0068</v>
+        <v>23.3684</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2554</v>
+        <v>1.0199</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7543</v>
+        <v>0.7385</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4988</v>
+        <v>0.2814</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.0798</v>
+        <v>-3.1043</v>
       </c>
       <c r="W12" t="n">
-        <v>3.6183</v>
+        <v>3.788</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.6981</v>
+        <v>-6.8922</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.4542</v>
+        <v>5.5074</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3306</v>
+        <v>2.861</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1237</v>
+        <v>2.6464</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5566</v>
+        <v>0.4841</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2581</v>
+        <v>-0.2335</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8147</v>
+        <v>0.7175</v>
       </c>
       <c r="J13" t="n">
-        <v>0.189</v>
+        <v>0.347</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5071</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3181</v>
+        <v>-0.2998</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3676</v>
+        <v>0.1371</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7652</v>
+        <v>-0.8802</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1328</v>
+        <v>1.0173</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4989</v>
+        <v>1.5023</v>
       </c>
       <c r="T13" t="n">
-        <v>4.0838</v>
+        <v>1.2451</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4151</v>
+        <v>0.2572</v>
       </c>
       <c r="V13" t="n">
-        <v>4.7991</v>
+        <v>4.8842</v>
       </c>
       <c r="W13" t="n">
-        <v>5.0589</v>
+        <v>5.1637</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="14">
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0095</v>
+        <v>1.1703</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.8993</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4455</v>
+        <v>0.271</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7068</v>
+        <v>0.695</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.173</v>
+        <v>-0.1966</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8799</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6218</v>
+        <v>0.6529</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6018</v>
+        <v>0.6323</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0422</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.193</v>
+        <v>-0.2171</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2781</v>
+        <v>0.2592</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1026</v>
+        <v>0.2806</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0578</v>
+        <v>0.2464</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1604</v>
+        <v>0.0341</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8451</v>
+        <v>0.8938</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8393</v>
+        <v>-0.2925</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6844</v>
+        <v>1.1863</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1867</v>
+        <v>2.1861</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2705</v>
+        <v>-0.3218</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4572</v>
+        <v>2.5079</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9889</v>
+        <v>3.1596</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3796</v>
+        <v>1.4163</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6093</v>
+        <v>1.7433</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8022</v>
+        <v>-0.9735</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6501</v>
+        <v>-1.7381</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8479</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1991</v>
+        <v>0.1809</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3466</v>
+        <v>-0.1163</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5457</v>
+        <v>0.2972</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3934</v>
+        <v>0.6744</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1726</v>
+        <v>1.3497</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7792</v>
+        <v>-0.6753</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3806</v>
+        <v>1.3382</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.384</v>
+        <v>-1.4271</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7646</v>
+        <v>2.7653</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5596</v>
+        <v>2.5947</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4796</v>
+        <v>2.5126</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.179</v>
+        <v>-1.2565</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4639</v>
+        <v>-1.5092</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2849</v>
+        <v>0.2527</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.387</v>
+        <v>-0.0796</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3867</v>
+        <v>-0.2713</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0002</v>
+        <v>0.1917</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2396</v>
+        <v>0.5009</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3171</v>
+        <v>-1.4665</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5567</v>
+        <v>1.9674</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2952</v>
+        <v>0.7916</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9528</v>
+        <v>0.2063</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3424</v>
+        <v>0.5853</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.2283</v>
+        <v>0.9019</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9161</v>
+        <v>0.9418</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3122</v>
+        <v>-0.0399</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9331</v>
+        <v>-0.1103</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0367</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9698</v>
+        <v>0.6251</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2003</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.8947</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2003</v>
+        <v>2.3368</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3345</v>
+        <v>-0.2333</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0888</v>
+        <v>0.0259</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4232</v>
+        <v>-0.2591</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PEREZ REQUENA</t>
+          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5541</v>
+        <v>0.4476</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5349</v>
+        <v>-1.8863</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.089</v>
+        <v>2.3338</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6642</v>
+        <v>-1.3261</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5042</v>
+        <v>-0.9971</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.16</v>
+        <v>-0.329</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9216</v>
+        <v>-2.117</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9597</v>
+        <v>-0.8774</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0381</v>
+        <v>-1.2396</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5858</v>
+        <v>0.791</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4639</v>
+        <v>-0.1197</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1219</v>
+        <v>0.9106</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4001</v>
+        <v>1.1684</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4001</v>
+        <v>1.1684</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2901</v>
+        <v>0.6052</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3867</v>
+        <v>0.2307</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.3745</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>A. PEREZ REQUENA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9336</v>
+        <v>-0.4357</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8848</v>
+        <v>0.5982</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9511</v>
+        <v>-1.0339</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7573</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1887</v>
+        <v>-0.5239</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5687</v>
+        <v>-0.1621</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6747</v>
+        <v>0.9692</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8252</v>
+        <v>0.9853</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1505</v>
+        <v>-0.0161</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08260000000000001</v>
+        <v>-1.6552</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6365</v>
+        <v>-1.5092</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7191</v>
+        <v>-0.146</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6005</v>
+        <v>0.3895</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.0011</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4007</v>
+        <v>0.3895</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5501</v>
+        <v>-0.1391</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0179</v>
+        <v>-0.371</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5322</v>
+        <v>0.2319</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6687</v>
+        <v>-1.0872</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3487</v>
+        <v>-1.9733</v>
       </c>
       <c r="F21" t="n">
-        <v>0.68</v>
+        <v>0.8862</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4553</v>
+        <v>-1.4845</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.4357</v>
+        <v>-2.4374</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9804</v>
+        <v>0.953</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3886</v>
+        <v>-1.2544</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3924</v>
+        <v>-1.3033</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0038</v>
+        <v>0.0489</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0667</v>
+        <v>-0.2301</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0433</v>
+        <v>-1.1342</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9766</v>
+        <v>0.9041</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4135</v>
+        <v>0.2026</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0401</v>
+        <v>0.2547</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4536</v>
+        <v>-0.0522</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4178</v>
+        <v>-1.9847</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.683</v>
+        <v>-2.4133</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2653</v>
+        <v>0.4286</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.211</v>
+        <v>-1.2258</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.851</v>
+        <v>-0.8611</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3599</v>
+        <v>-0.3647</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.296</v>
+        <v>-1.268</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.658</v>
+        <v>-0.644</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M22" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0422</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.193</v>
+        <v>-0.2171</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2781</v>
+        <v>0.2592</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6066</v>
+        <v>-0.1747</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3867</v>
+        <v>-0.1717</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2199</v>
+        <v>-0.003</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4967</v>
+        <v>-4.5765</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1984</v>
+        <v>-3.4371</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2983</v>
+        <v>-1.1394</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3169</v>
+        <v>-2.3974</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.4641</v>
+        <v>-3.5058</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1473</v>
+        <v>1.1085</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1494</v>
+        <v>0.2748</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2142</v>
+        <v>-1.1519</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3636</v>
+        <v>1.4268</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4662</v>
+        <v>-2.6722</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.2499</v>
+        <v>-2.3539</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2163</v>
+        <v>-0.3183</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6002</v>
+        <v>-0.5618</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3469</v>
+        <v>-0.7909</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2533</v>
+        <v>0.2291</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.668200000000001</v>
+        <v>-8.6364</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.1771</v>
+        <v>-6.8191</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4911</v>
+        <v>-1.8172</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7754</v>
+        <v>-1.7882</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2829</v>
+        <v>-1.2351</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4925</v>
+        <v>-0.5531</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2309</v>
+        <v>-0.083</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1672</v>
+        <v>0.2978</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.398</v>
+        <v>-0.3808</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5446</v>
+        <v>-1.7051</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4501</v>
+        <v>-1.5329</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0945</v>
+        <v>-0.1723</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.0017</v>
+        <v>-5.8421</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0322</v>
+        <v>-0.0371</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6044</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5722</v>
+        <v>0.5258</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.6593</v>
+        <v>-2.7216</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3192</v>
+        <v>-2.3905</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.597499999999999</v>
+        <v>-6.310300000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.6465</v>
+        <v>-11.3641</v>
       </c>
       <c r="F25" t="n">
-        <v>6.049100000000001</v>
+        <v>5.053900000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.9302</v>
+        <v>-2.197200000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-11.3876</v>
+        <v>-11.5331</v>
       </c>
       <c r="I25" t="n">
-        <v>9.457799999999999</v>
+        <v>9.335999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>4.161</v>
+        <v>5.3935</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2419000000000004</v>
+        <v>0.4139000000000003</v>
       </c>
       <c r="L25" t="n">
-        <v>4.403</v>
+        <v>4.979499999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.0912</v>
+        <v>-7.590400000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-11.1456</v>
+        <v>-11.947</v>
       </c>
       <c r="O25" t="n">
-        <v>5.0546</v>
+        <v>4.3562</v>
       </c>
       <c r="P25" t="n">
-        <v>-9.002600000000001</v>
+        <v>-8.763200000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-24.0068</v>
+        <v>-23.3683</v>
       </c>
       <c r="R25" t="n">
-        <v>15.0041</v>
+        <v>14.6052</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2554000000000001</v>
+        <v>1.546</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4985999999999999</v>
+        <v>-0.2814</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7541</v>
+        <v>1.8272</v>
       </c>
       <c r="V25" t="n">
-        <v>3.079800000000001</v>
+        <v>3.104199999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>6.698</v>
+        <v>6.8921</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.6182</v>
+        <v>-3.7879</v>
       </c>
     </row>
   </sheetData>
